--- a/ismd-backend-validator/src/test/resources/com/dia/canonical/complete/testExcelProject_no-lkod.xlsx
+++ b/ismd-backend-validator/src/test/resources/com/dia/canonical/complete/testExcelProject_no-lkod.xlsx
@@ -31,7 +31,7 @@
     <t>Název slovníku:</t>
   </si>
   <si>
-    <t>Slovník dle metodiky dat Digitální a informační agentury</t>
+    <t>Příkladový slovník z metodiky popisu dat</t>
   </si>
   <si>
     <t>Popis slovníku:</t>
